--- a/data/raw/benv_exports/peste_americana_2026_italia.xlsx
+++ b/data/raw/benv_exports/peste_americana_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>84562</v>
+        <v>84930</v>
       </c>
       <c r="B2" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -423,10 +423,10 @@
         <v>E</v>
       </c>
       <c r="D2" t="str">
-        <v>18/05/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>11/05/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F2" t="str">
         <v>19/06/2026</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>84514</v>
+        <v>84562</v>
       </c>
       <c r="B3" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -458,13 +458,13 @@
         <v>E</v>
       </c>
       <c r="D3" t="str">
-        <v>14/05/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>05/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>18/05/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -473,18 +473,18 @@
         <v>APE</v>
       </c>
       <c r="I3" t="str">
-        <v>PALU\'</v>
+        <v>PIANORO</v>
       </c>
       <c r="J3" t="str">
-        <v>VR</v>
+        <v>BO</v>
       </c>
       <c r="K3" t="str">
-        <v>VENETO</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>84930</v>
+        <v>84514</v>
       </c>
       <c r="B4" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -493,13 +493,13 @@
         <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>29/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>29/05/2026</v>
+        <v>05/05/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>19/06/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -508,18 +508,18 @@
         <v>APE</v>
       </c>
       <c r="I4" t="str">
-        <v>PIANORO</v>
+        <v>PALU\'</v>
       </c>
       <c r="J4" t="str">
-        <v>BO</v>
+        <v>VR</v>
       </c>
       <c r="K4" t="str">
-        <v>EMILIA ROMAGNA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>85491</v>
+        <v>85715</v>
       </c>
       <c r="B5" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -528,10 +528,10 @@
         <v>C</v>
       </c>
       <c r="D5" t="str">
-        <v>07/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>06/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="F5" t="str">
         <v>-</v>
@@ -543,18 +543,18 @@
         <v>APE</v>
       </c>
       <c r="I5" t="str">
-        <v>TUBRE - TAUFERS IM MUENSTERTAL</v>
+        <v>CERVETERI</v>
       </c>
       <c r="J5" t="str">
-        <v>BZ</v>
+        <v>RM</v>
       </c>
       <c r="K5" t="str">
-        <v>TRENTINO ALTO ADIGE</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>85484</v>
+        <v>85491</v>
       </c>
       <c r="B6" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -563,10 +563,10 @@
         <v>C</v>
       </c>
       <c r="D6" t="str">
-        <v>03/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>23/06/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="F6" t="str">
         <v>-</v>
@@ -578,18 +578,53 @@
         <v>APE</v>
       </c>
       <c r="I6" t="str">
+        <v>TUBRE - TAUFERS IM MUENSTERTAL</v>
+      </c>
+      <c r="J6" t="str">
+        <v>BZ</v>
+      </c>
+      <c r="K6" t="str">
+        <v>TRENTINO ALTO ADIGE</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>85484</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C7" t="str">
+        <v>C</v>
+      </c>
+      <c r="D7" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="E7" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="F7" t="str">
+        <v>-</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>APE</v>
+      </c>
+      <c r="I7" t="str">
         <v>FELTRE</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J7" t="str">
         <v>BL</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K7" t="str">
         <v>VENETO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>